--- a/document/struct/document.xlsx
+++ b/document/struct/document.xlsx
@@ -74,15 +74,7 @@
     <t xml:space="preserve">¶</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Document Process Manager (DPM) ministrates web projects:  
+    <t xml:space="preserve">Document Process Manager (DPM) ministrates web projects:  
  - Document Piler (File/Database Piler)
    - Markup Piler
    - Style Piler
@@ -91,108 +83,12 @@
  - Document Generator (File/Database Generator)
    - Document Generator Interfacing
    - Document Generator Modeling
-   - </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Document </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Generator Templating
+   - Document Generator Templating
  - Document System (File/Database System)
-   - Document </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">System </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Server
-   - Document </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">System </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Router
-   - Document </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">System </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Web Socket
-   - Document </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">System </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Web Browser</t>
-    </r>
+   - Document System Server
+   - Document System Router
+   - Document System Web Socket
+   - Document System Web Browser</t>
   </si>
   <si>
     <t xml:space="preserve">Impetus</t>
@@ -230,7 +126,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -265,12 +161,6 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -354,7 +244,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -675,12 +565,8 @@
         <f aca="false">_xlfn.CONCAT($A$1, ".", $B$2, ".", $A9)</f>
         <v>DOC.0.SEGID.6</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>21</v>
-      </c>
+      <c r="C9" s="3"/>
+      <c r="D9" s="4"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
@@ -690,14 +576,14 @@
         <f aca="false">_xlfn.CONCAT($A$1, ".", $B$2, ".", $A10)</f>
         <v>DOC.0.SEGID.7</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C10" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
         <v>8</v>
       </c>
@@ -705,14 +591,14 @@
         <f aca="false">_xlfn.CONCAT($A$1, ".", $B$2, ".", $A11)</f>
         <v>DOC.0.SEGID.8</v>
       </c>
-      <c r="C11" s="8" t="s">
-        <v>23</v>
+      <c r="C11" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
         <v>9</v>
       </c>
@@ -720,11 +606,11 @@
         <f aca="false">_xlfn.CONCAT($A$1, ".", $B$2, ".", $A12)</f>
         <v>DOC.0.SEGID.9</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>25</v>
+      <c r="C12" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -739,7 +625,7 @@
         <v>14</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -749,6 +635,12 @@
       <c r="B14" s="1" t="str">
         <f aca="false">_xlfn.CONCAT($A$1, ".", $B$2, ".", $A14)</f>
         <v>DOC.0.SEGID.11</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
